--- a/doc et autres/données Excel.xlsx
+++ b/doc et autres/données Excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Arnaud\Documents\GitHub\lemark_website\doc et autres\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{276DBE45-83AB-4CBF-9184-FAFA4D12CE69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9ADDCB0-350A-45D1-8813-EFE9428952D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11596" xr2:uid="{F9DCC1AC-59D4-4FD4-8A43-4172AFD5FE19}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14620" xr2:uid="{F9DCC1AC-59D4-4FD4-8A43-4172AFD5FE19}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="135">
   <si>
     <t>id_categorie</t>
   </si>
@@ -131,17 +131,326 @@
     <t>Description longue</t>
   </si>
   <si>
-    <t>Nom</t>
-  </si>
-  <si>
-    <t>est_actif</t>
+    <t>Categorie</t>
+  </si>
+  <si>
+    <t>Produit</t>
+  </si>
+  <si>
+    <t>id_option</t>
+  </si>
+  <si>
+    <t>nom_option</t>
+  </si>
+  <si>
+    <t>sku</t>
+  </si>
+  <si>
+    <t>description_option</t>
+  </si>
+  <si>
+    <t>Re-Surfaceur</t>
+  </si>
+  <si>
+    <t>Traceur-Pro</t>
+  </si>
+  <si>
+    <t>Traceur-Eco</t>
+  </si>
+  <si>
+    <t>Grattoir</t>
+  </si>
+  <si>
+    <t>Roues</t>
+  </si>
+  <si>
+    <t>Ski SkimarkTD</t>
+  </si>
+  <si>
+    <t>Déflecteurs</t>
+  </si>
+  <si>
+    <t>S-O-RESU</t>
+  </si>
+  <si>
+    <t>S-O-TRPR</t>
+  </si>
+  <si>
+    <t>S-O-TREC</t>
+  </si>
+  <si>
+    <t>S-O-GRAT</t>
+  </si>
+  <si>
+    <t>S-O-ROUE</t>
+  </si>
+  <si>
+    <t>RC-O-SKIS</t>
+  </si>
+  <si>
+    <t>NH-O-ROUE</t>
+  </si>
+  <si>
+    <t>NH-O-DEFL</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Options_Equipement</t>
+  </si>
+  <si>
+    <t>Modele</t>
+  </si>
+  <si>
+    <t>id_modele</t>
+  </si>
+  <si>
+    <t>nom_modele</t>
+  </si>
+  <si>
+    <t>specifications</t>
+  </si>
+  <si>
+    <t>S-SF36</t>
+  </si>
+  <si>
+    <t>S-SF48</t>
+  </si>
+  <si>
+    <t>S-SF60</t>
+  </si>
+  <si>
+    <t>S-SP36</t>
+  </si>
+  <si>
+    <t>S-SP48</t>
+  </si>
+  <si>
+    <t>S-SP72</t>
+  </si>
+  <si>
+    <t>S-SP84</t>
+  </si>
+  <si>
+    <t>S-SP60</t>
+  </si>
+  <si>
+    <t>RC-SF60</t>
+  </si>
+  <si>
+    <t>RC-SF96</t>
+  </si>
+  <si>
+    <t>RC-ST48</t>
+  </si>
+  <si>
+    <t>RC-ST54</t>
+  </si>
+  <si>
+    <t>RC-SN54</t>
+  </si>
+  <si>
+    <t>DF-TS99</t>
+  </si>
+  <si>
+    <t>RM-D3060SP</t>
+  </si>
+  <si>
+    <t>RM-D3060TP</t>
+  </si>
+  <si>
+    <t>RM-D3672TP</t>
+  </si>
+  <si>
+    <t>RM-D4872TP</t>
+  </si>
+  <si>
+    <t>RM-D4872TM</t>
+  </si>
+  <si>
+    <t>RM-B4848SM</t>
+  </si>
+  <si>
+    <t>RM-B3060SP</t>
+  </si>
+  <si>
+    <t>RM-B4872TM</t>
+  </si>
+  <si>
+    <t>RM-H3060T</t>
+  </si>
+  <si>
+    <t>RM-DT99</t>
+  </si>
+  <si>
+    <t>RM-JD99</t>
+  </si>
+  <si>
+    <t>RM-TT99</t>
+  </si>
+  <si>
+    <t>NH-LM48</t>
+  </si>
+  <si>
+    <t>NH-LM60</t>
+  </si>
+  <si>
+    <t>NH-LM72</t>
+  </si>
+  <si>
+    <t>NH-LM72X3</t>
+  </si>
+  <si>
+    <t>NH-H4</t>
+  </si>
+  <si>
+    <t>NH-H5</t>
+  </si>
+  <si>
+    <t>F-M20</t>
+  </si>
+  <si>
+    <t>F-M26</t>
+  </si>
+  <si>
+    <t>F-M36</t>
+  </si>
+  <si>
+    <t>SF36</t>
+  </si>
+  <si>
+    <t>SF48</t>
+  </si>
+  <si>
+    <t>SF60</t>
+  </si>
+  <si>
+    <t>SP36</t>
+  </si>
+  <si>
+    <t>SP48</t>
+  </si>
+  <si>
+    <t>SP60</t>
+  </si>
+  <si>
+    <t>SP72</t>
+  </si>
+  <si>
+    <t>SP84</t>
+  </si>
+  <si>
+    <t>SF96</t>
+  </si>
+  <si>
+    <t>ST48</t>
+  </si>
+  <si>
+    <t>ST54</t>
+  </si>
+  <si>
+    <t>SN54</t>
+  </si>
+  <si>
+    <t>TS99</t>
+  </si>
+  <si>
+    <t>D3060SP</t>
+  </si>
+  <si>
+    <t>D3060TP</t>
+  </si>
+  <si>
+    <t>D3672TP</t>
+  </si>
+  <si>
+    <t>D4872TP</t>
+  </si>
+  <si>
+    <t>D4872TM</t>
+  </si>
+  <si>
+    <t>B4848SM</t>
+  </si>
+  <si>
+    <t>B3060SP</t>
+  </si>
+  <si>
+    <t>B4872TM</t>
+  </si>
+  <si>
+    <t>H3060T</t>
+  </si>
+  <si>
+    <t>DT99</t>
+  </si>
+  <si>
+    <t>JD99</t>
+  </si>
+  <si>
+    <t>TT99</t>
+  </si>
+  <si>
+    <t>LM48</t>
+  </si>
+  <si>
+    <t>LM60</t>
+  </si>
+  <si>
+    <t>LM72</t>
+  </si>
+  <si>
+    <t>LM72X3</t>
+  </si>
+  <si>
+    <t>H4</t>
+  </si>
+  <si>
+    <t>H5</t>
+  </si>
+  <si>
+    <t>M20</t>
+  </si>
+  <si>
+    <t>M26</t>
+  </si>
+  <si>
+    <t>M36</t>
+  </si>
+  <si>
+    <t>NH-H3</t>
+  </si>
+  <si>
+    <t>H3</t>
+  </si>
+  <si>
+    <t>Largeur x Profondeur</t>
+  </si>
+  <si>
+    <t>COMPTATIBLE</t>
+  </si>
+  <si>
+    <t>Image_Produit</t>
+  </si>
+  <si>
+    <t>id_image</t>
+  </si>
+  <si>
+    <t>ordre_affichage</t>
+  </si>
+  <si>
+    <t>nom_fichier</t>
+  </si>
+  <si>
+    <t>nom_fichier_image</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -153,6 +462,12 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -515,22 +830,58 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{651DD8E5-9EFA-437B-9B91-58D1DCC552A6}">
-  <dimension ref="C5:L38"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="C4:AH41"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="9.06640625" customWidth="1"/>
-    <col min="3" max="3" width="14.3984375" customWidth="1"/>
-    <col min="4" max="4" width="22.46484375" customWidth="1"/>
-    <col min="6" max="6" width="10.59765625" customWidth="1"/>
-    <col min="7" max="7" width="25.9296875" customWidth="1"/>
-    <col min="8" max="8" width="17.46484375" customWidth="1"/>
+    <col min="2" max="2" width="9.08984375" customWidth="1"/>
+    <col min="3" max="3" width="14.36328125" customWidth="1"/>
+    <col min="4" max="4" width="22.453125" customWidth="1"/>
+    <col min="6" max="6" width="10.6328125" customWidth="1"/>
+    <col min="7" max="7" width="25.90625" customWidth="1"/>
+    <col min="8" max="8" width="17.453125" customWidth="1"/>
     <col min="9" max="9" width="22" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
-    <col min="11" max="11" width="11.33203125" customWidth="1"/>
-    <col min="12" max="12" width="10.73046875" customWidth="1"/>
+    <col min="11" max="11" width="11.36328125" customWidth="1"/>
+    <col min="12" max="12" width="10.7265625" customWidth="1"/>
+    <col min="14" max="14" width="10.36328125" customWidth="1"/>
+    <col min="15" max="15" width="13.453125" customWidth="1"/>
+    <col min="16" max="16" width="13.26953125" customWidth="1"/>
+    <col min="17" max="19" width="21" customWidth="1"/>
+    <col min="20" max="20" width="13.6328125" customWidth="1"/>
+    <col min="21" max="21" width="13.7265625" customWidth="1"/>
+    <col min="22" max="22" width="17.453125" customWidth="1"/>
+    <col min="23" max="23" width="19.36328125" customWidth="1"/>
+    <col min="24" max="24" width="14.26953125" customWidth="1"/>
+    <col min="27" max="27" width="12.90625" customWidth="1"/>
+    <col min="28" max="28" width="12" customWidth="1"/>
+    <col min="30" max="30" width="14.7265625" customWidth="1"/>
+    <col min="31" max="31" width="10.6328125" customWidth="1"/>
+    <col min="32" max="32" width="10.36328125" customWidth="1"/>
+    <col min="33" max="33" width="15.1796875" customWidth="1"/>
+    <col min="34" max="34" width="11.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="3:12" x14ac:dyDescent="0.45">
+    <row r="4" spans="3:34" x14ac:dyDescent="0.35">
+      <c r="C4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AA4" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="AD4" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="5" spans="3:34" x14ac:dyDescent="0.35">
       <c r="C5" s="1" t="s">
         <v>0</v>
       </c>
@@ -555,11 +906,61 @@
       <c r="K5" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="L5" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="3:12" x14ac:dyDescent="0.45">
+      <c r="L5" s="1"/>
+      <c r="N5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="R5" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="S5" s="1"/>
+      <c r="T5" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="U5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="V5" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="W5" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="X5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD5" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="AE5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF5" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="AG5" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="AH5" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="6" spans="3:34" x14ac:dyDescent="0.35">
       <c r="C6">
         <v>1</v>
       </c>
@@ -579,16 +980,46 @@
         <v>29</v>
       </c>
       <c r="J6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6">
         <v>1</v>
       </c>
-      <c r="L6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="3:12" x14ac:dyDescent="0.45">
+      <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6" t="s">
+        <v>36</v>
+      </c>
+      <c r="P6" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>51</v>
+      </c>
+      <c r="T6">
+        <v>1</v>
+      </c>
+      <c r="U6" t="s">
+        <v>57</v>
+      </c>
+      <c r="V6" t="s">
+        <v>92</v>
+      </c>
+      <c r="W6" t="s">
+        <v>128</v>
+      </c>
+      <c r="X6">
+        <v>1</v>
+      </c>
+      <c r="AA6">
+        <v>1</v>
+      </c>
+      <c r="AB6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="3:34" x14ac:dyDescent="0.35">
       <c r="C7">
         <v>2</v>
       </c>
@@ -608,16 +1039,46 @@
         <v>29</v>
       </c>
       <c r="J7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7">
         <v>1</v>
       </c>
-      <c r="L7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="3:12" x14ac:dyDescent="0.45">
+      <c r="N7">
+        <v>2</v>
+      </c>
+      <c r="O7" t="s">
+        <v>37</v>
+      </c>
+      <c r="P7" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>51</v>
+      </c>
+      <c r="T7">
+        <v>2</v>
+      </c>
+      <c r="U7" t="s">
+        <v>58</v>
+      </c>
+      <c r="V7" t="s">
+        <v>93</v>
+      </c>
+      <c r="W7" t="s">
+        <v>128</v>
+      </c>
+      <c r="X7">
+        <v>1</v>
+      </c>
+      <c r="AA7">
+        <v>2</v>
+      </c>
+      <c r="AB7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="3:34" x14ac:dyDescent="0.35">
       <c r="C8">
         <v>3</v>
       </c>
@@ -628,7 +1089,7 @@
         <v>3</v>
       </c>
       <c r="G8" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H8" t="s">
         <v>28</v>
@@ -637,16 +1098,46 @@
         <v>29</v>
       </c>
       <c r="J8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8">
-        <v>1</v>
-      </c>
-      <c r="L8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="3:12" x14ac:dyDescent="0.45">
+        <v>2</v>
+      </c>
+      <c r="N8">
+        <v>3</v>
+      </c>
+      <c r="O8" t="s">
+        <v>38</v>
+      </c>
+      <c r="P8" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>51</v>
+      </c>
+      <c r="T8">
+        <v>3</v>
+      </c>
+      <c r="U8" t="s">
+        <v>59</v>
+      </c>
+      <c r="V8" t="s">
+        <v>94</v>
+      </c>
+      <c r="W8" t="s">
+        <v>128</v>
+      </c>
+      <c r="X8">
+        <v>1</v>
+      </c>
+      <c r="AA8">
+        <v>2</v>
+      </c>
+      <c r="AB8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="3:34" x14ac:dyDescent="0.35">
       <c r="C9">
         <v>4</v>
       </c>
@@ -657,7 +1148,7 @@
         <v>4</v>
       </c>
       <c r="G9" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="H9" t="s">
         <v>28</v>
@@ -666,16 +1157,46 @@
         <v>29</v>
       </c>
       <c r="J9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9">
-        <v>1</v>
-      </c>
-      <c r="L9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="3:12" x14ac:dyDescent="0.45">
+        <v>2</v>
+      </c>
+      <c r="N9">
+        <v>4</v>
+      </c>
+      <c r="O9" t="s">
+        <v>39</v>
+      </c>
+      <c r="P9" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>51</v>
+      </c>
+      <c r="T9">
+        <v>4</v>
+      </c>
+      <c r="U9" t="s">
+        <v>60</v>
+      </c>
+      <c r="V9" t="s">
+        <v>95</v>
+      </c>
+      <c r="W9" t="s">
+        <v>128</v>
+      </c>
+      <c r="X9">
+        <v>2</v>
+      </c>
+      <c r="AA9">
+        <v>2</v>
+      </c>
+      <c r="AB9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="3:34" x14ac:dyDescent="0.35">
       <c r="C10">
         <v>5</v>
       </c>
@@ -686,7 +1207,7 @@
         <v>5</v>
       </c>
       <c r="G10" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="H10" t="s">
         <v>28</v>
@@ -695,16 +1216,46 @@
         <v>29</v>
       </c>
       <c r="J10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10">
-        <v>1</v>
-      </c>
-      <c r="L10" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="3:12" x14ac:dyDescent="0.45">
+        <v>2</v>
+      </c>
+      <c r="N10">
+        <v>5</v>
+      </c>
+      <c r="O10" t="s">
+        <v>40</v>
+      </c>
+      <c r="P10" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>51</v>
+      </c>
+      <c r="T10">
+        <v>5</v>
+      </c>
+      <c r="U10" t="s">
+        <v>61</v>
+      </c>
+      <c r="V10" t="s">
+        <v>96</v>
+      </c>
+      <c r="W10" t="s">
+        <v>128</v>
+      </c>
+      <c r="X10">
+        <v>2</v>
+      </c>
+      <c r="AA10">
+        <v>2</v>
+      </c>
+      <c r="AB10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="3:34" x14ac:dyDescent="0.35">
       <c r="C11">
         <v>6</v>
       </c>
@@ -715,7 +1266,7 @@
         <v>6</v>
       </c>
       <c r="G11" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H11" t="s">
         <v>28</v>
@@ -724,21 +1275,51 @@
         <v>29</v>
       </c>
       <c r="J11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11">
+        <v>3</v>
+      </c>
+      <c r="N11">
+        <v>6</v>
+      </c>
+      <c r="O11" t="s">
+        <v>41</v>
+      </c>
+      <c r="P11" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>51</v>
+      </c>
+      <c r="T11">
+        <v>6</v>
+      </c>
+      <c r="U11" t="s">
+        <v>64</v>
+      </c>
+      <c r="V11" t="s">
+        <v>97</v>
+      </c>
+      <c r="W11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X11">
         <v>2</v>
       </c>
-      <c r="L11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="3:12" x14ac:dyDescent="0.45">
+      <c r="AA11">
+        <v>7</v>
+      </c>
+      <c r="AB11">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="3:34" x14ac:dyDescent="0.35">
       <c r="F12">
         <v>7</v>
       </c>
       <c r="G12" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H12" t="s">
         <v>28</v>
@@ -747,21 +1328,51 @@
         <v>29</v>
       </c>
       <c r="J12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12">
+        <v>4</v>
+      </c>
+      <c r="N12">
+        <v>7</v>
+      </c>
+      <c r="O12" t="s">
+        <v>40</v>
+      </c>
+      <c r="P12" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>51</v>
+      </c>
+      <c r="T12">
+        <v>7</v>
+      </c>
+      <c r="U12" t="s">
+        <v>62</v>
+      </c>
+      <c r="V12" t="s">
+        <v>98</v>
+      </c>
+      <c r="W12" t="s">
+        <v>128</v>
+      </c>
+      <c r="X12">
         <v>2</v>
       </c>
-      <c r="L12" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="3:12" x14ac:dyDescent="0.45">
+      <c r="AA12">
+        <v>8</v>
+      </c>
+      <c r="AB12">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="3:34" x14ac:dyDescent="0.35">
       <c r="F13">
         <v>8</v>
       </c>
       <c r="G13" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H13" t="s">
         <v>28</v>
@@ -770,21 +1381,51 @@
         <v>29</v>
       </c>
       <c r="J13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13">
+        <v>4</v>
+      </c>
+      <c r="N13">
+        <v>8</v>
+      </c>
+      <c r="O13" t="s">
+        <v>42</v>
+      </c>
+      <c r="P13" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>51</v>
+      </c>
+      <c r="T13">
+        <v>8</v>
+      </c>
+      <c r="U13" t="s">
+        <v>63</v>
+      </c>
+      <c r="V13" t="s">
+        <v>99</v>
+      </c>
+      <c r="W13" t="s">
+        <v>128</v>
+      </c>
+      <c r="X13">
         <v>2</v>
       </c>
-      <c r="L13" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="3:12" x14ac:dyDescent="0.45">
+      <c r="AA13">
+        <v>9</v>
+      </c>
+      <c r="AB13">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="3:34" x14ac:dyDescent="0.35">
       <c r="F14">
         <v>9</v>
       </c>
       <c r="G14" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H14" t="s">
         <v>28</v>
@@ -793,21 +1434,39 @@
         <v>29</v>
       </c>
       <c r="J14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14">
-        <v>2</v>
-      </c>
-      <c r="L14" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="3:12" x14ac:dyDescent="0.45">
+        <v>4</v>
+      </c>
+      <c r="T14">
+        <v>9</v>
+      </c>
+      <c r="U14" t="s">
+        <v>65</v>
+      </c>
+      <c r="V14" t="s">
+        <v>94</v>
+      </c>
+      <c r="W14" t="s">
+        <v>128</v>
+      </c>
+      <c r="X14">
+        <v>3</v>
+      </c>
+      <c r="AA14">
+        <v>10</v>
+      </c>
+      <c r="AB14">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="3:34" x14ac:dyDescent="0.35">
       <c r="F15">
         <v>10</v>
       </c>
       <c r="G15" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H15" t="s">
         <v>28</v>
@@ -816,21 +1475,39 @@
         <v>29</v>
       </c>
       <c r="J15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15">
-        <v>2</v>
-      </c>
-      <c r="L15" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="3:12" x14ac:dyDescent="0.45">
+        <v>4</v>
+      </c>
+      <c r="T15">
+        <v>10</v>
+      </c>
+      <c r="U15" t="s">
+        <v>66</v>
+      </c>
+      <c r="V15" t="s">
+        <v>100</v>
+      </c>
+      <c r="W15" t="s">
+        <v>128</v>
+      </c>
+      <c r="X15">
+        <v>3</v>
+      </c>
+      <c r="AA15">
+        <v>11</v>
+      </c>
+      <c r="AB15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="3:34" x14ac:dyDescent="0.35">
       <c r="F16">
         <v>11</v>
       </c>
       <c r="G16" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H16" t="s">
         <v>28</v>
@@ -839,21 +1516,39 @@
         <v>29</v>
       </c>
       <c r="J16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16">
-        <v>2</v>
-      </c>
-      <c r="L16" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="6:12" x14ac:dyDescent="0.45">
+        <v>4</v>
+      </c>
+      <c r="T16">
+        <v>11</v>
+      </c>
+      <c r="U16" t="s">
+        <v>67</v>
+      </c>
+      <c r="V16" t="s">
+        <v>101</v>
+      </c>
+      <c r="W16" t="s">
+        <v>128</v>
+      </c>
+      <c r="X16">
+        <v>4</v>
+      </c>
+      <c r="AA16">
+        <v>13</v>
+      </c>
+      <c r="AB16">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="6:28" x14ac:dyDescent="0.35">
       <c r="F17">
         <v>12</v>
       </c>
       <c r="G17" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="H17" t="s">
         <v>28</v>
@@ -862,21 +1557,39 @@
         <v>29</v>
       </c>
       <c r="J17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17">
-        <v>3</v>
-      </c>
-      <c r="L17" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="6:12" x14ac:dyDescent="0.45">
+        <v>4</v>
+      </c>
+      <c r="T17">
+        <v>12</v>
+      </c>
+      <c r="U17" t="s">
+        <v>68</v>
+      </c>
+      <c r="V17" t="s">
+        <v>102</v>
+      </c>
+      <c r="W17" t="s">
+        <v>128</v>
+      </c>
+      <c r="X17">
+        <v>4</v>
+      </c>
+      <c r="AA17">
+        <v>14</v>
+      </c>
+      <c r="AB17">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="6:28" x14ac:dyDescent="0.35">
       <c r="F18">
         <v>13</v>
       </c>
       <c r="G18" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H18" t="s">
         <v>28</v>
@@ -885,21 +1598,33 @@
         <v>29</v>
       </c>
       <c r="J18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18">
-        <v>3</v>
-      </c>
-      <c r="L18" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="6:12" x14ac:dyDescent="0.45">
+        <v>5</v>
+      </c>
+      <c r="T18">
+        <v>13</v>
+      </c>
+      <c r="U18" t="s">
+        <v>69</v>
+      </c>
+      <c r="V18" t="s">
+        <v>103</v>
+      </c>
+      <c r="W18" t="s">
+        <v>128</v>
+      </c>
+      <c r="X18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="6:28" x14ac:dyDescent="0.35">
       <c r="F19">
         <v>14</v>
       </c>
       <c r="G19" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="H19" t="s">
         <v>28</v>
@@ -908,21 +1633,33 @@
         <v>29</v>
       </c>
       <c r="J19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19">
-        <v>3</v>
-      </c>
-      <c r="L19" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="6:12" x14ac:dyDescent="0.45">
+        <v>5</v>
+      </c>
+      <c r="T19">
+        <v>14</v>
+      </c>
+      <c r="U19" t="s">
+        <v>70</v>
+      </c>
+      <c r="V19" t="s">
+        <v>104</v>
+      </c>
+      <c r="W19" t="s">
+        <v>128</v>
+      </c>
+      <c r="X19">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="6:28" x14ac:dyDescent="0.35">
       <c r="F20">
         <v>15</v>
       </c>
       <c r="G20" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H20" t="s">
         <v>28</v>
@@ -931,430 +1668,386 @@
         <v>29</v>
       </c>
       <c r="J20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20">
-        <v>3</v>
-      </c>
-      <c r="L20" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="6:12" x14ac:dyDescent="0.45">
-      <c r="F21">
+        <v>6</v>
+      </c>
+      <c r="T20">
+        <v>15</v>
+      </c>
+      <c r="U20" t="s">
+        <v>71</v>
+      </c>
+      <c r="V20" t="s">
+        <v>105</v>
+      </c>
+      <c r="W20" t="s">
+        <v>128</v>
+      </c>
+      <c r="X20">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="6:28" x14ac:dyDescent="0.35">
+      <c r="T21">
         <v>16</v>
       </c>
-      <c r="G21" t="s">
+      <c r="U21" t="s">
+        <v>72</v>
+      </c>
+      <c r="V21" t="s">
+        <v>106</v>
+      </c>
+      <c r="W21" t="s">
+        <v>128</v>
+      </c>
+      <c r="X21">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="6:28" x14ac:dyDescent="0.35">
+      <c r="T22">
+        <v>17</v>
+      </c>
+      <c r="U22" t="s">
+        <v>73</v>
+      </c>
+      <c r="V22" t="s">
+        <v>107</v>
+      </c>
+      <c r="W22" t="s">
+        <v>128</v>
+      </c>
+      <c r="X22">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="6:28" x14ac:dyDescent="0.35">
+      <c r="T23">
+        <v>18</v>
+      </c>
+      <c r="U23" t="s">
+        <v>74</v>
+      </c>
+      <c r="V23" t="s">
+        <v>108</v>
+      </c>
+      <c r="W23" t="s">
+        <v>128</v>
+      </c>
+      <c r="X23">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="6:28" x14ac:dyDescent="0.35">
+      <c r="T24">
         <v>19</v>
       </c>
-      <c r="H21" t="s">
+      <c r="U24" t="s">
+        <v>75</v>
+      </c>
+      <c r="V24" t="s">
+        <v>109</v>
+      </c>
+      <c r="W24" t="s">
+        <v>128</v>
+      </c>
+      <c r="X24">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="6:28" x14ac:dyDescent="0.35">
+      <c r="T25">
+        <v>20</v>
+      </c>
+      <c r="U25" t="s">
+        <v>76</v>
+      </c>
+      <c r="V25" t="s">
+        <v>110</v>
+      </c>
+      <c r="W25" t="s">
+        <v>128</v>
+      </c>
+      <c r="X25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="6:28" x14ac:dyDescent="0.35">
+      <c r="T26">
+        <v>21</v>
+      </c>
+      <c r="U26" t="s">
+        <v>77</v>
+      </c>
+      <c r="V26" t="s">
+        <v>111</v>
+      </c>
+      <c r="W26" t="s">
+        <v>128</v>
+      </c>
+      <c r="X26">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="6:28" x14ac:dyDescent="0.35">
+      <c r="T27">
+        <v>22</v>
+      </c>
+      <c r="U27" t="s">
+        <v>78</v>
+      </c>
+      <c r="V27" t="s">
+        <v>112</v>
+      </c>
+      <c r="W27" t="s">
+        <v>128</v>
+      </c>
+      <c r="X27">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="6:28" x14ac:dyDescent="0.35">
+      <c r="T28">
+        <v>23</v>
+      </c>
+      <c r="U28" t="s">
+        <v>79</v>
+      </c>
+      <c r="V28" t="s">
+        <v>113</v>
+      </c>
+      <c r="W28" t="s">
+        <v>128</v>
+      </c>
+      <c r="X28">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" spans="6:28" x14ac:dyDescent="0.35">
+      <c r="T29">
+        <v>24</v>
+      </c>
+      <c r="U29" t="s">
+        <v>80</v>
+      </c>
+      <c r="V29" t="s">
+        <v>114</v>
+      </c>
+      <c r="W29" t="s">
+        <v>128</v>
+      </c>
+      <c r="X29">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="6:28" x14ac:dyDescent="0.35">
+      <c r="T30">
+        <v>25</v>
+      </c>
+      <c r="U30" t="s">
+        <v>81</v>
+      </c>
+      <c r="V30" t="s">
+        <v>115</v>
+      </c>
+      <c r="W30" t="s">
+        <v>128</v>
+      </c>
+      <c r="X30">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="6:28" x14ac:dyDescent="0.35">
+      <c r="T31">
+        <v>26</v>
+      </c>
+      <c r="U31" t="s">
+        <v>82</v>
+      </c>
+      <c r="V31" t="s">
+        <v>116</v>
+      </c>
+      <c r="W31" t="s">
+        <v>128</v>
+      </c>
+      <c r="X31">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32" spans="6:28" x14ac:dyDescent="0.35">
+      <c r="T32">
+        <v>27</v>
+      </c>
+      <c r="U32" t="s">
+        <v>83</v>
+      </c>
+      <c r="V32" t="s">
+        <v>117</v>
+      </c>
+      <c r="W32" t="s">
+        <v>128</v>
+      </c>
+      <c r="X32">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" spans="20:24" x14ac:dyDescent="0.35">
+      <c r="T33">
         <v>28</v>
       </c>
-      <c r="I21" t="s">
+      <c r="U33" t="s">
+        <v>84</v>
+      </c>
+      <c r="V33" t="s">
+        <v>118</v>
+      </c>
+      <c r="W33" t="s">
+        <v>128</v>
+      </c>
+      <c r="X33">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34" spans="20:24" x14ac:dyDescent="0.35">
+      <c r="T34">
         <v>29</v>
       </c>
-      <c r="J21" t="b">
-        <v>0</v>
-      </c>
-      <c r="K21">
-        <v>4</v>
-      </c>
-      <c r="L21" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="6:12" x14ac:dyDescent="0.45">
-      <c r="F22">
-        <v>17</v>
-      </c>
-      <c r="G22" t="s">
-        <v>20</v>
-      </c>
-      <c r="H22" t="s">
-        <v>28</v>
-      </c>
-      <c r="I22" t="s">
-        <v>29</v>
-      </c>
-      <c r="J22" t="b">
-        <v>0</v>
-      </c>
-      <c r="K22">
-        <v>4</v>
-      </c>
-      <c r="L22" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="6:12" x14ac:dyDescent="0.45">
-      <c r="F23">
-        <v>18</v>
-      </c>
-      <c r="G23" t="s">
-        <v>21</v>
-      </c>
-      <c r="H23" t="s">
-        <v>28</v>
-      </c>
-      <c r="I23" t="s">
-        <v>29</v>
-      </c>
-      <c r="J23" t="b">
-        <v>0</v>
-      </c>
-      <c r="K23">
-        <v>4</v>
-      </c>
-      <c r="L23" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="6:12" x14ac:dyDescent="0.45">
-      <c r="F24">
-        <v>19</v>
-      </c>
-      <c r="G24" t="s">
-        <v>22</v>
-      </c>
-      <c r="H24" t="s">
-        <v>28</v>
-      </c>
-      <c r="I24" t="s">
-        <v>29</v>
-      </c>
-      <c r="J24" t="b">
-        <v>0</v>
-      </c>
-      <c r="K24">
-        <v>4</v>
-      </c>
-      <c r="L24" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="6:12" x14ac:dyDescent="0.45">
-      <c r="F25">
-        <v>20</v>
-      </c>
-      <c r="G25" t="s">
-        <v>23</v>
-      </c>
-      <c r="H25" t="s">
-        <v>28</v>
-      </c>
-      <c r="I25" t="s">
-        <v>29</v>
-      </c>
-      <c r="J25" t="b">
-        <v>0</v>
-      </c>
-      <c r="K25">
-        <v>4</v>
-      </c>
-      <c r="L25" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="6:12" x14ac:dyDescent="0.45">
-      <c r="F26">
-        <v>21</v>
-      </c>
-      <c r="G26" t="s">
-        <v>24</v>
-      </c>
-      <c r="H26" t="s">
-        <v>28</v>
-      </c>
-      <c r="I26" t="s">
-        <v>29</v>
-      </c>
-      <c r="J26" t="b">
-        <v>0</v>
-      </c>
-      <c r="K26">
-        <v>4</v>
-      </c>
-      <c r="L26" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="6:12" x14ac:dyDescent="0.45">
-      <c r="F27">
-        <v>22</v>
-      </c>
-      <c r="G27" t="s">
+      <c r="U34" t="s">
+        <v>85</v>
+      </c>
+      <c r="V34" t="s">
+        <v>119</v>
+      </c>
+      <c r="W34" t="s">
+        <v>128</v>
+      </c>
+      <c r="X34">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35" spans="20:24" x14ac:dyDescent="0.35">
+      <c r="T35">
         <v>30</v>
       </c>
-      <c r="H27" t="s">
-        <v>28</v>
-      </c>
-      <c r="I27" t="s">
-        <v>29</v>
-      </c>
-      <c r="J27" t="b">
-        <v>0</v>
-      </c>
-      <c r="K27">
-        <v>4</v>
-      </c>
-      <c r="L27" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="6:12" x14ac:dyDescent="0.45">
-      <c r="F28">
-        <v>23</v>
-      </c>
-      <c r="G28" t="s">
-        <v>30</v>
-      </c>
-      <c r="H28" t="s">
-        <v>28</v>
-      </c>
-      <c r="I28" t="s">
-        <v>29</v>
-      </c>
-      <c r="J28" t="b">
-        <v>0</v>
-      </c>
-      <c r="K28">
-        <v>4</v>
-      </c>
-      <c r="L28" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="6:12" x14ac:dyDescent="0.45">
-      <c r="F29">
-        <v>24</v>
-      </c>
-      <c r="G29" t="s">
-        <v>30</v>
-      </c>
-      <c r="H29" t="s">
-        <v>28</v>
-      </c>
-      <c r="I29" t="s">
-        <v>29</v>
-      </c>
-      <c r="J29" t="b">
-        <v>0</v>
-      </c>
-      <c r="K29">
-        <v>4</v>
-      </c>
-      <c r="L29" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="6:12" x14ac:dyDescent="0.45">
-      <c r="F30">
-        <v>25</v>
-      </c>
-      <c r="G30" t="s">
-        <v>25</v>
-      </c>
-      <c r="H30" t="s">
-        <v>28</v>
-      </c>
-      <c r="I30" t="s">
-        <v>29</v>
-      </c>
-      <c r="J30" t="b">
-        <v>0</v>
-      </c>
-      <c r="K30">
-        <v>5</v>
-      </c>
-      <c r="L30" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="6:12" x14ac:dyDescent="0.45">
-      <c r="F31">
-        <v>26</v>
-      </c>
-      <c r="G31" t="s">
-        <v>26</v>
-      </c>
-      <c r="H31" t="s">
-        <v>28</v>
-      </c>
-      <c r="I31" t="s">
-        <v>29</v>
-      </c>
-      <c r="J31" t="b">
-        <v>0</v>
-      </c>
-      <c r="K31">
-        <v>5</v>
-      </c>
-      <c r="L31" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="6:12" x14ac:dyDescent="0.45">
-      <c r="F32">
-        <v>27</v>
-      </c>
-      <c r="G32" t="s">
-        <v>30</v>
-      </c>
-      <c r="H32" t="s">
-        <v>28</v>
-      </c>
-      <c r="I32" t="s">
-        <v>29</v>
-      </c>
-      <c r="J32" t="b">
-        <v>0</v>
-      </c>
-      <c r="K32">
-        <v>5</v>
-      </c>
-      <c r="L32" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="6:12" x14ac:dyDescent="0.45">
-      <c r="F33">
-        <v>28</v>
-      </c>
-      <c r="G33" t="s">
-        <v>30</v>
-      </c>
-      <c r="H33" t="s">
-        <v>28</v>
-      </c>
-      <c r="I33" t="s">
-        <v>29</v>
-      </c>
-      <c r="J33" t="b">
-        <v>0</v>
-      </c>
-      <c r="K33">
-        <v>5</v>
-      </c>
-      <c r="L33" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="6:12" x14ac:dyDescent="0.45">
-      <c r="F34">
-        <v>29</v>
-      </c>
-      <c r="G34" t="s">
-        <v>30</v>
-      </c>
-      <c r="H34" t="s">
-        <v>28</v>
-      </c>
-      <c r="I34" t="s">
-        <v>29</v>
-      </c>
-      <c r="J34" t="b">
-        <v>0</v>
-      </c>
-      <c r="K34">
-        <v>5</v>
-      </c>
-      <c r="L34" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="6:12" x14ac:dyDescent="0.45">
-      <c r="F35">
-        <v>30</v>
-      </c>
-      <c r="G35" t="s">
-        <v>27</v>
-      </c>
-      <c r="H35" t="s">
-        <v>28</v>
-      </c>
-      <c r="I35" t="s">
-        <v>29</v>
-      </c>
-      <c r="J35" t="b">
-        <v>0</v>
-      </c>
-      <c r="K35">
-        <v>6</v>
-      </c>
-      <c r="L35" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="6:12" x14ac:dyDescent="0.45">
-      <c r="F36">
+      <c r="U35" t="s">
+        <v>86</v>
+      </c>
+      <c r="V35" t="s">
+        <v>120</v>
+      </c>
+      <c r="W35" t="s">
+        <v>128</v>
+      </c>
+      <c r="X35">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36" spans="20:24" x14ac:dyDescent="0.35">
+      <c r="T36">
         <v>31</v>
       </c>
-      <c r="G36" t="s">
-        <v>30</v>
-      </c>
-      <c r="H36" t="s">
-        <v>28</v>
-      </c>
-      <c r="I36" t="s">
-        <v>29</v>
-      </c>
-      <c r="J36" t="b">
-        <v>0</v>
-      </c>
-      <c r="K36">
-        <v>6</v>
-      </c>
-      <c r="L36" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="6:12" x14ac:dyDescent="0.45">
-      <c r="F37">
+      <c r="U36" t="s">
+        <v>126</v>
+      </c>
+      <c r="V36" t="s">
+        <v>127</v>
+      </c>
+      <c r="W36" t="s">
+        <v>128</v>
+      </c>
+      <c r="X36">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37" spans="20:24" x14ac:dyDescent="0.35">
+      <c r="T37">
         <v>32</v>
       </c>
-      <c r="G37" t="s">
-        <v>30</v>
-      </c>
-      <c r="H37" t="s">
-        <v>28</v>
-      </c>
-      <c r="I37" t="s">
-        <v>29</v>
-      </c>
-      <c r="J37" t="b">
-        <v>0</v>
-      </c>
-      <c r="K37">
-        <v>6</v>
-      </c>
-      <c r="L37" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="6:12" x14ac:dyDescent="0.45">
-      <c r="F38">
+      <c r="U37" t="s">
+        <v>87</v>
+      </c>
+      <c r="V37" t="s">
+        <v>121</v>
+      </c>
+      <c r="W37" t="s">
+        <v>128</v>
+      </c>
+      <c r="X37">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" spans="20:24" x14ac:dyDescent="0.35">
+      <c r="T38">
         <v>33</v>
       </c>
-      <c r="G38" t="s">
-        <v>30</v>
-      </c>
-      <c r="H38" t="s">
-        <v>28</v>
-      </c>
-      <c r="I38" t="s">
-        <v>29</v>
-      </c>
-      <c r="J38" t="b">
-        <v>0</v>
-      </c>
-      <c r="K38">
-        <v>6</v>
-      </c>
-      <c r="L38" t="b">
-        <v>0</v>
+      <c r="U38" t="s">
+        <v>88</v>
+      </c>
+      <c r="V38" t="s">
+        <v>122</v>
+      </c>
+      <c r="W38" t="s">
+        <v>128</v>
+      </c>
+      <c r="X38">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="39" spans="20:24" x14ac:dyDescent="0.35">
+      <c r="T39">
+        <v>34</v>
+      </c>
+      <c r="U39" t="s">
+        <v>89</v>
+      </c>
+      <c r="V39" t="s">
+        <v>123</v>
+      </c>
+      <c r="W39" t="s">
+        <v>128</v>
+      </c>
+      <c r="X39">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40" spans="20:24" x14ac:dyDescent="0.35">
+      <c r="T40">
+        <v>35</v>
+      </c>
+      <c r="U40" t="s">
+        <v>90</v>
+      </c>
+      <c r="V40" t="s">
+        <v>124</v>
+      </c>
+      <c r="W40" t="s">
+        <v>128</v>
+      </c>
+      <c r="X40">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41" spans="20:24" x14ac:dyDescent="0.35">
+      <c r="T41">
+        <v>36</v>
+      </c>
+      <c r="U41" t="s">
+        <v>91</v>
+      </c>
+      <c r="V41" t="s">
+        <v>125</v>
+      </c>
+      <c r="W41" t="s">
+        <v>128</v>
+      </c>
+      <c r="X41">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>